--- a/resultados/saojeronimodaserra/erros_varredura.xlsx
+++ b/resultados/saojeronimodaserra/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -868,6 +868,2694 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2706%2F&amp;fileName=daz7K00ey1A4P0mgTH_bHUCR8-WTDEwC.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:00:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/departamento/exportar-txt?id=6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F73%2F&amp;fileName=IQA2JInBGf-o0jKhxmV4kFgx53uyCjJp.pdf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:17:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/exportar-csv?id=355</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-14 14:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>404</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:37:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>404</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:37:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>404</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>404</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:41:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/conta/index</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>404</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:43:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:52:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/impressao?id=2742</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/impressao?id=2742</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2742</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2742</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2742</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2742</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-14 15:53:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>404</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:39:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>404</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>404</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-14 16:40:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>404</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:20:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>404</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:20:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>404</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:20:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4225%2F&amp;fileName=Lo5PIJMQOhvF9dE60fsAVGImhx_yj4VG.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:44:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:51:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:51:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:58:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:00:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>500</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:01:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:02:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>500</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:03:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/documento/exportar-txt?id=93</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:11:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3941%2F&amp;fileName=iwzgck-uWlb7Fd63h2SxfVGA4_ISENWA.pdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:42:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2929%2F&amp;fileName=EFvoCGXoHvtJ1TG-8aUDVIDu75tIABJ3.pdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-14 19:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2937%2F&amp;fileName=kP92IskFzP5WVgFzlT49oDTEd29E2g_X.pdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3130%2F&amp;fileName=FFWESiSHickwgXUm_aECZwK0mtvITcGe.pdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-14 20:14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4655%2F&amp;fileName=AsqgA3_zWFtnEocuh_k0YpikERkOyEpw.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:19:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4658%2F&amp;fileName=2NVZyJnhvk-GAOAsPaVUq8AdyZQzHWTE.pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:35:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>500</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:09:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>500</v>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:10:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>500</v>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:10:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>500</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:10:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>500</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:11:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>500</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:11:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>500</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>500</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:12:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>500</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>500</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>500</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:13:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>500</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:13:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>500</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:14:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>500</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>500</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:15:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>500</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>500</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>500</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:16:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>500</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:16:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>500</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:17:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:17:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>500</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>500</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>500</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>500</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:18:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>500</v>
+      </c>
+      <c r="E85" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:19:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>500</v>
+      </c>
+      <c r="E86" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:20:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>500</v>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:20:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>500</v>
+      </c>
+      <c r="E88" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:25:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>500</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:26:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>500</v>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>500</v>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:26:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>500</v>
+      </c>
+      <c r="E92" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:27:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>500</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>500</v>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:28:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>500</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:28:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>404</v>
+      </c>
+      <c r="E98" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:57:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>404</v>
+      </c>
+      <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:57:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>404</v>
+      </c>
+      <c r="E100" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:57:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>404</v>
+      </c>
+      <c r="E101" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:57:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>500</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-15 02:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>500</v>
+      </c>
+      <c r="E103" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-15 02:00:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>404</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-15 04:10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4553%2F&amp;fileName=-L4N2Wnt8ADrv1SLdv4lK2XC9N-XRomE.pdf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-15 05:12:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4689%2F&amp;fileName=DhJDFkOej1a5nzvq_5o2Gfgu1E5gKw3-.pdf</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-15 05:30:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:37:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:40:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:43:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:48:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-15 06:50:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saojeronimodaserra/erros_varredura.xlsx
+++ b/resultados/saojeronimodaserra/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3556,6 +3556,62 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2467</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:39:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2437</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-15 10:13:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saojeronimodaserra/erros_varredura.xlsx
+++ b/resultados/saojeronimodaserra/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3612,6 +3612,5074 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-15 14:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-15 14:55:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-15 14:58:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:01:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:10:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:19:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:22:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:24:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:28:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:31:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:34:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:37:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:39:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:43:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:46:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:49:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:52:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-08-15 15:58:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:01:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:04:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:07:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:10:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:15:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:23:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>4</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>4</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:29:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>4</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:33:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:37:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>4</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:40:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:44:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>500</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:46:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:49:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>4</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:53:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>4</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-08-15 16:56:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>4</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:00:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>4</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:04:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>404</v>
+      </c>
+      <c r="E156" t="n">
+        <v>4</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:14:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>404</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:14:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>500</v>
+      </c>
+      <c r="E158" t="n">
+        <v>5</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:27:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>500</v>
+      </c>
+      <c r="E159" t="n">
+        <v>5</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:28:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>500</v>
+      </c>
+      <c r="E160" t="n">
+        <v>5</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:28:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>500</v>
+      </c>
+      <c r="E161" t="n">
+        <v>5</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:29:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>500</v>
+      </c>
+      <c r="E162" t="n">
+        <v>5</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:29:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>500</v>
+      </c>
+      <c r="E163" t="n">
+        <v>5</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:29:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>500</v>
+      </c>
+      <c r="E164" t="n">
+        <v>5</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:29:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>500</v>
+      </c>
+      <c r="E165" t="n">
+        <v>5</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:31:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>500</v>
+      </c>
+      <c r="E166" t="n">
+        <v>5</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:31:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>500</v>
+      </c>
+      <c r="E167" t="n">
+        <v>5</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>500</v>
+      </c>
+      <c r="E168" t="n">
+        <v>5</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:33:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>500</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:33:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>500</v>
+      </c>
+      <c r="E170" t="n">
+        <v>5</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:34:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>500</v>
+      </c>
+      <c r="E171" t="n">
+        <v>5</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:34:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>500</v>
+      </c>
+      <c r="E172" t="n">
+        <v>5</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:34:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>500</v>
+      </c>
+      <c r="E173" t="n">
+        <v>5</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:34:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>500</v>
+      </c>
+      <c r="E174" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>500</v>
+      </c>
+      <c r="E175" t="n">
+        <v>5</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:35:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>500</v>
+      </c>
+      <c r="E176" t="n">
+        <v>5</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:36:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>500</v>
+      </c>
+      <c r="E177" t="n">
+        <v>5</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:36:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>500</v>
+      </c>
+      <c r="E178" t="n">
+        <v>5</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:36:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>500</v>
+      </c>
+      <c r="E179" t="n">
+        <v>5</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:37:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>500</v>
+      </c>
+      <c r="E180" t="n">
+        <v>5</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:37:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>500</v>
+      </c>
+      <c r="E181" t="n">
+        <v>5</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:38:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>500</v>
+      </c>
+      <c r="E182" t="n">
+        <v>5</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:38:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>500</v>
+      </c>
+      <c r="E183" t="n">
+        <v>5</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:38:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>500</v>
+      </c>
+      <c r="E184" t="n">
+        <v>5</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>500</v>
+      </c>
+      <c r="E185" t="n">
+        <v>5</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:39:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>500</v>
+      </c>
+      <c r="E186" t="n">
+        <v>5</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:39:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>500</v>
+      </c>
+      <c r="E187" t="n">
+        <v>5</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:40:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>500</v>
+      </c>
+      <c r="E188" t="n">
+        <v>5</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:40:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>500</v>
+      </c>
+      <c r="E189" t="n">
+        <v>5</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:40:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>500</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:40:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>500</v>
+      </c>
+      <c r="E191" t="n">
+        <v>5</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:41:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>500</v>
+      </c>
+      <c r="E192" t="n">
+        <v>5</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:42:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>5</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-08-15 17:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>5</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>5</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-08-15 19:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2629</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>5</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:38:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2704</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>5</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2701</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>5</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2696</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>5</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2696</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>5</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:24:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2699</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>5</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:25:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4790%2F&amp;fileName=S-5a79hl6E2wdPJbdt2mV69ZElOljS5i.pdf</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>5</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:28:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2695</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>5</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:28:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2695</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>5</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:28:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4785%2F&amp;fileName=ABgO3MmorlJmlKpE1JYt4kOV-R0FRzdW.pdf</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>5</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:28:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2693</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>5</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:28:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2671</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>5</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:30:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4717%2F&amp;fileName=8lJ9zH6oQlTMgNV5WYswielFpU-Jd7-h.pdf</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>5</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:32:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4716%2F&amp;fileName=UXgIPCyyW4CTzlqHTFbev87gVLm3tL-J.pdf</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>5</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:32:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2673</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>5</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:32:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4730%2F&amp;fileName=sBIlP8G4kRim6DjdOQbdmK0YAiYOwweF.pdf</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>5</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:32:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2651</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>5</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:47:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2646</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>5</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:49:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2645</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>5</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:49:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2644</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>5</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:50:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2644</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>5</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:50:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2643</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>5</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-08-16 00:50:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>5</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-08-16 04:43:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>5</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-08-16 04:48:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>5</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-08-16 04:51:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>5</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-08-16 04:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>5</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:00:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>5</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:03:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>5</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:06:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>5</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:09:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>5</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>5</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>5</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:18:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>5</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>5</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:24:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>5</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:27:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>5</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:30:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>5</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>5</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:36:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>5</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:39:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>5</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:42:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:45:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>5</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>5</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:51:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>5</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:54:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>5</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-08-16 05:58:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>5</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:01:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>5</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:03:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>5</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:09:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>5</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:17:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>5</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:21:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>5</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:27:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>5</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:31:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>5</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:35:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>500</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:38:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>500</v>
+      </c>
+      <c r="E252" t="n">
+        <v>5</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:38:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>5</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>5</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:44:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>5</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:48:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>5</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:51:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>5</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:55:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>5</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>500</v>
+      </c>
+      <c r="E259" t="n">
+        <v>5</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-08-16 07:00:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fnoticia%2F2515%2F&amp;fileName=KNqDTWHas_PUi2G77U45744qPToGyks-.pdf</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/exportar-csv?id=60</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>5</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-08-16 10:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F3316%2F&amp;fileName=Afjy5wpfMIhSJL1NmftWF0WHcrrcTOWi.pdf</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>6</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-08-16 12:17:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/formulario/view/4/fale-conosco-2</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>404</v>
+      </c>
+      <c r="E263" t="n">
+        <v>6</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:49:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>404</v>
+      </c>
+      <c r="E264" t="n">
+        <v>6</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:50:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta/logout</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>404</v>
+      </c>
+      <c r="E265" t="n">
+        <v>6</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-08-16 13:50:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2063</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>7</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-08-16 20:13:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2062</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>7</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-08-16 20:35:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2053</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>7</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F2548%2F&amp;fileName=88DHZz_EzdewK_OA7biNC-OU5XLTGN2Z.pdf</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>7</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-08-16 21:52:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2047</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>7</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-08-16 22:36:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2258</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>7</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-08-16 23:44:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>404</v>
+      </c>
+      <c r="E272" t="n">
+        <v>7</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>404</v>
+      </c>
+      <c r="E273" t="n">
+        <v>7</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:13:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>404</v>
+      </c>
+      <c r="E274" t="n">
+        <v>7</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:16:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>7</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:19:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta/index</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>404</v>
+      </c>
+      <c r="E276" t="n">
+        <v>7</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:34:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/exportar-txt?id=107</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>7</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2026-08-17 02:00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F261%2F&amp;fileName=Lj_f0GzZ8ezXqD908-JXSf1euHVZCLjL.pdf</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>7</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2026-08-17 02:52:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>404</v>
+      </c>
+      <c r="E279" t="n">
+        <v>8</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:41:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>404</v>
+      </c>
+      <c r="E280" t="n">
+        <v>8</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:42:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>404</v>
+      </c>
+      <c r="E281" t="n">
+        <v>8</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:42:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>500</v>
+      </c>
+      <c r="E282" t="n">
+        <v>8</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:45:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>500</v>
+      </c>
+      <c r="E283" t="n">
+        <v>8</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:45:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>500</v>
+      </c>
+      <c r="E284" t="n">
+        <v>8</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:45:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3151%2F&amp;fileName=lu3xk3zyyNqMPh6jBy1EAZmiYDalzW5H.pdf</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>8</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:50:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/departamento/exportar-csv?id=16</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>8</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:56:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4256%2F&amp;fileName=FuG4kRaMKrwxbGzvLUKFLaXZOzFW4u9U.pdf</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>8</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:42:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4258%2F&amp;fileName=4GK1v_Rs0iZLZOoCpvwdBcMlfu4Z1I0F.pdf</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>8</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:47:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fentidade%2F25%2F&amp;fileName=Ql1LkQPoot0af2Tf_Hqjn5PaPTb-fvHW.pdf</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>8</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:28:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>404</v>
+      </c>
+      <c r="E290" t="n">
+        <v>8</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2026-08-17 11:33:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>404</v>
+      </c>
+      <c r="E291" t="n">
+        <v>8</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>404</v>
+      </c>
+      <c r="E292" t="n">
+        <v>8</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>404</v>
+      </c>
+      <c r="E293" t="n">
+        <v>8</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:24:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>404</v>
+      </c>
+      <c r="E294" t="n">
+        <v>8</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:24:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>404</v>
+      </c>
+      <c r="E295" t="n">
+        <v>8</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-08-17 12:24:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saojeronimodaserra/erros_varredura.xlsx
+++ b/resultados/saojeronimodaserra/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F295"/>
+  <dimension ref="A1:F366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-12 08:47:03</t>
+          <t>2026-08-12 08:50:50</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-12 08:50:50</t>
+          <t>2026-08-12 08:56:06</t>
         </is>
       </c>
     </row>
@@ -764,23 +764,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/conta/index</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12 08:54:23</t>
+          <t>2026-08-12 09:13:52</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -804,11 +804,11 @@
         <v>404</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12 08:56:06</t>
+          <t>2026-08-14 15:37:17</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/conta/index</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -832,11 +832,11 @@
         <v>404</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12 09:13:52</t>
+          <t>2026-08-14 15:37:23</t>
         </is>
       </c>
     </row>
@@ -848,23 +848,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/departamento/exportar-txt?id=21</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-12 09:28:29</t>
+          <t>2026-08-14 15:41:11</t>
         </is>
       </c>
     </row>
@@ -876,23 +876,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2706%2F&amp;fileName=daz7K00ey1A4P0mgTH_bHUCR8-WTDEwC.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14 14:00:30</t>
+          <t>2026-08-14 15:41:16</t>
         </is>
       </c>
     </row>
@@ -904,23 +904,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/departamento/exportar-txt?id=6</t>
+          <t>https://saojeronimodaserra.pr.gov.br/conta/index</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14 14:13:24</t>
+          <t>2026-08-14 15:43:54</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F73%2F&amp;fileName=IQA2JInBGf-o0jKhxmV4kFgx53uyCjJp.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-14 14:17:07</t>
+          <t>2026-08-14 15:52:36</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/exportar-csv?id=355</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-14 14:22:29</t>
+          <t>2026-08-14 15:52:49</t>
         </is>
       </c>
     </row>
@@ -988,23 +988,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/impressao?id=2742</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14 15:37:17</t>
+          <t>2026-08-14 15:53:02</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2742</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14 15:37:23</t>
+          <t>2026-08-14 15:53:15</t>
         </is>
       </c>
     </row>
@@ -1044,23 +1044,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2742</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14 15:41:11</t>
+          <t>2026-08-14 15:53:29</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-14 15:41:16</t>
+          <t>2026-08-14 16:39:33</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/conta/index</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14 15:43:54</t>
+          <t>2026-08-14 16:40:07</t>
         </is>
       </c>
     </row>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:35</t>
+          <t>2026-08-14 16:40:40</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:36</t>
+          <t>2026-08-14 17:20:11</t>
         </is>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:48</t>
+          <t>2026-08-14 17:20:16</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4881%2F&amp;fileName=EAcW1fWYNbxZ8rbXwryua2-Ic1BtbsOM.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14 15:52:49</t>
+          <t>2026-08-14 17:20:17</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/impressao?id=2742</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:01</t>
+          <t>2026-08-14 18:51:47</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/impressao?id=2742</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:02</t>
+          <t>2026-08-14 19:01:15</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2742</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:14</t>
+          <t>2026-08-14 19:03:43</t>
         </is>
       </c>
     </row>
@@ -1324,23 +1324,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2742</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:15</t>
+          <t>2026-08-14 23:10:57</t>
         </is>
       </c>
     </row>
@@ -1352,23 +1352,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2742</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:27</t>
+          <t>2026-08-14 23:12:49</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1380,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2742</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14 15:53:29</t>
+          <t>2026-08-14 23:13:38</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14 16:39:33</t>
+          <t>2026-08-14 23:15:35</t>
         </is>
       </c>
     </row>
@@ -1436,23 +1436,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14 16:40:07</t>
+          <t>2026-08-14 23:18:31</t>
         </is>
       </c>
     </row>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14 16:40:40</t>
+          <t>2026-08-14 23:26:35</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1492,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14 17:20:11</t>
+          <t>2026-08-14 23:28:32</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1532,11 +1532,11 @@
         <v>404</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14 17:20:16</t>
+          <t>2026-08-15 01:57:11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1560,11 +1560,11 @@
         <v>404</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14 17:20:17</t>
+          <t>2026-08-15 01:57:16</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1576,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4225%2F&amp;fileName=Lo5PIJMQOhvF9dE60fsAVGImhx_yj4VG.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14 18:44:47</t>
+          <t>2026-08-15 01:57:17</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1604,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-14 18:51:45</t>
+          <t>2026-08-15 01:57:51</t>
         </is>
       </c>
     </row>
@@ -1632,23 +1632,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-14 18:51:47</t>
+          <t>2026-08-15 04:10:04</t>
         </is>
       </c>
     </row>
@@ -1660,23 +1660,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14 18:53:14</t>
+          <t>2026-08-15 17:14:21</t>
         </is>
       </c>
     </row>
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14 18:56:37</t>
+          <t>2026-08-15 17:14:39</t>
         </is>
       </c>
     </row>
@@ -1716,23 +1716,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14 18:58:28</t>
+          <t>2026-08-15 17:29:56</t>
         </is>
       </c>
     </row>
@@ -1744,23 +1744,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14 19:00:37</t>
+          <t>2026-08-15 17:34:05</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1784,11 +1784,11 @@
         <v>500</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14 19:01:15</t>
+          <t>2026-08-15 17:36:07</t>
         </is>
       </c>
     </row>
@@ -1800,23 +1800,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14 19:02:58</t>
+          <t>2026-08-15 17:38:17</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1840,11 +1840,11 @@
         <v>500</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14 19:03:43</t>
+          <t>2026-08-15 17:40:23</t>
         </is>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/documento/exportar-txt?id=93</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14 19:11:26</t>
+          <t>2026-08-16 06:38:37</t>
         </is>
       </c>
     </row>
@@ -1884,23 +1884,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3941%2F&amp;fileName=iwzgck-uWlb7Fd63h2SxfVGA4_ISENWA.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14 19:42:14</t>
+          <t>2026-08-16 07:00:16</t>
         </is>
       </c>
     </row>
@@ -1912,23 +1912,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2929%2F&amp;fileName=EFvoCGXoHvtJ1TG-8aUDVIDu75tIABJ3.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/formulario/view/4/fale-conosco-2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-14 19:48:35</t>
+          <t>2026-08-16 13:49:44</t>
         </is>
       </c>
     </row>
@@ -1940,23 +1940,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2937%2F&amp;fileName=kP92IskFzP5WVgFzlT49oDTEd29E2g_X.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-14 20:05:54</t>
+          <t>2026-08-16 13:50:13</t>
         </is>
       </c>
     </row>
@@ -1968,23 +1968,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3130%2F&amp;fileName=FFWESiSHickwgXUm_aECZwK0mtvITcGe.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta/logout</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14 20:14:17</t>
+          <t>2026-08-16 13:50:48</t>
         </is>
       </c>
     </row>
@@ -1996,23 +1996,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4655%2F&amp;fileName=AsqgA3_zWFtnEocuh_k0YpikERkOyEpw.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14 21:19:31</t>
+          <t>2026-08-17 01:13:22</t>
         </is>
       </c>
     </row>
@@ -2024,23 +2024,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4658%2F&amp;fileName=2NVZyJnhvk-GAOAsPaVUq8AdyZQzHWTE.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14 21:35:18</t>
+          <t>2026-08-17 01:13:28</t>
         </is>
       </c>
     </row>
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14 23:09:37</t>
+          <t>2026-08-17 01:16:23</t>
         </is>
       </c>
     </row>
@@ -2080,23 +2080,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/conta/index</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14 23:10:11</t>
+          <t>2026-08-17 01:34:16</t>
         </is>
       </c>
     </row>
@@ -2108,23 +2108,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14 23:10:46</t>
+          <t>2026-08-17 08:41:48</t>
         </is>
       </c>
     </row>
@@ -2136,23 +2136,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14 23:10:57</t>
+          <t>2026-08-17 08:42:22</t>
         </is>
       </c>
     </row>
@@ -2164,23 +2164,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-14 23:10:58</t>
+          <t>2026-08-17 08:42:57</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2204,11 +2204,11 @@
         <v>500</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14 23:11:21</t>
+          <t>2026-08-17 08:45:48</t>
         </is>
       </c>
     </row>
@@ -2220,23 +2220,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14 23:11:57</t>
+          <t>2026-08-17 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2248,23 +2248,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14 23:12:32</t>
+          <t>2026-08-17 12:23:55</t>
         </is>
       </c>
     </row>
@@ -2276,23 +2276,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14 23:12:49</t>
+          <t>2026-08-17 12:24:05</t>
         </is>
       </c>
     </row>
@@ -2304,23 +2304,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14 23:12:50</t>
+          <t>2026-08-17 12:24:06</t>
         </is>
       </c>
     </row>
@@ -2332,23 +2332,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-14 23:13:24</t>
+          <t>2026-08-17 12:24:39</t>
         </is>
       </c>
     </row>
@@ -2360,23 +2360,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-14 23:13:38</t>
+          <t>2026-08-17 12:24:45</t>
         </is>
       </c>
     </row>
@@ -2388,23 +2388,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_504</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-14 23:13:38</t>
+          <t>2026-08-17 21:01:57</t>
         </is>
       </c>
     </row>
@@ -2416,23 +2416,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-14 23:14:13</t>
+          <t>2026-08-18 21:49:34</t>
         </is>
       </c>
     </row>
@@ -2444,23 +2444,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-14 23:14:44</t>
+          <t>2026-08-18 22:10:20</t>
         </is>
       </c>
     </row>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-14 23:15:18</t>
+          <t>2026-08-18 22:12:27</t>
         </is>
       </c>
     </row>
@@ -2500,23 +2500,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-14 23:15:35</t>
+          <t>2026-08-18 22:15:07</t>
         </is>
       </c>
     </row>
@@ -2528,23 +2528,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-14 23:15:36</t>
+          <t>2026-08-18 22:38:59</t>
         </is>
       </c>
     </row>
@@ -2556,23 +2556,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-14 23:16:10</t>
+          <t>2026-08-18 22:41:37</t>
         </is>
       </c>
     </row>
@@ -2584,23 +2584,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-14 23:16:41</t>
+          <t>2026-08-18 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2624,11 +2624,11 @@
         <v>500</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-14 23:17:16</t>
+          <t>2026-08-18 23:56:15</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2652,11 +2652,11 @@
         <v>500</v>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-14 23:17:51</t>
+          <t>2026-08-19 07:14:56</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2680,11 +2680,11 @@
         <v>500</v>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-14 23:18:25</t>
+          <t>2026-08-19 07:15:01</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2708,11 +2708,11 @@
         <v>500</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-14 23:18:31</t>
+          <t>2026-08-19 07:15:50</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2736,11 +2736,11 @@
         <v>500</v>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-14 23:18:31</t>
+          <t>2026-08-19 07:19:53</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2764,11 +2764,11 @@
         <v>500</v>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-14 23:18:56</t>
+          <t>2026-08-19 07:22:18</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2792,11 +2792,11 @@
         <v>500</v>
       </c>
       <c r="E85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-14 23:19:31</t>
+          <t>2026-08-19 07:23:10</t>
         </is>
       </c>
     </row>
@@ -2808,23 +2808,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-14 23:20:05</t>
+          <t>2026-08-20 03:22:47</t>
         </is>
       </c>
     </row>
@@ -2836,23 +2836,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-14 23:20:33</t>
+          <t>2026-08-20 03:25:03</t>
         </is>
       </c>
     </row>
@@ -2864,23 +2864,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-14 23:25:50</t>
+          <t>2026-08-20 03:31:16</t>
         </is>
       </c>
     </row>
@@ -2892,23 +2892,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-14 23:26:24</t>
+          <t>2026-08-20 03:33:32</t>
         </is>
       </c>
     </row>
@@ -2920,23 +2920,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-14 23:26:35</t>
+          <t>2026-08-20 03:35:49</t>
         </is>
       </c>
     </row>
@@ -2948,23 +2948,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-14 23:26:36</t>
+          <t>2026-08-20 03:38:05</t>
         </is>
       </c>
     </row>
@@ -2976,23 +2976,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-14 23:27:11</t>
+          <t>2026-08-20 03:40:21</t>
         </is>
       </c>
     </row>
@@ -3004,23 +3004,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-14 23:27:45</t>
+          <t>2026-08-20 03:42:37</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3044,11 +3044,11 @@
         <v>500</v>
       </c>
       <c r="E94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-14 23:28:14</t>
+          <t>2026-08-20 03:43:14</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-14 23:28:32</t>
+          <t>2026-08-20 03:46:02</t>
         </is>
       </c>
     </row>
@@ -3088,23 +3088,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E96" t="n">
         <v>4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-15 00:49:49</t>
+          <t>2026-08-20 03:46:37</t>
         </is>
       </c>
     </row>
@@ -3116,23 +3116,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E97" t="n">
         <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-15 00:51:52</t>
+          <t>2026-08-20 03:47:12</t>
         </is>
       </c>
     </row>
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E98" t="n">
         <v>4</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-15 01:57:11</t>
+          <t>2026-08-20 03:47:46</t>
         </is>
       </c>
     </row>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E99" t="n">
         <v>4</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-15 01:57:16</t>
+          <t>2026-08-20 03:47:56</t>
         </is>
       </c>
     </row>
@@ -3200,23 +3200,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E100" t="n">
         <v>4</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-15 01:57:17</t>
+          <t>2026-08-20 03:47:57</t>
         </is>
       </c>
     </row>
@@ -3228,23 +3228,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E101" t="n">
         <v>4</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-15 01:57:51</t>
+          <t>2026-08-20 03:48:31</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-15 02:00:00</t>
+          <t>2026-08-20 03:49:05</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-15 02:00:34</t>
+          <t>2026-08-20 03:49:40</t>
         </is>
       </c>
     </row>
@@ -3312,23 +3312,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E104" t="n">
         <v>4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-15 04:10:04</t>
+          <t>2026-08-20 03:50:14</t>
         </is>
       </c>
     </row>
@@ -3340,23 +3340,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4553%2F&amp;fileName=-L4N2Wnt8ADrv1SLdv4lK2XC9N-XRomE.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E105" t="n">
         <v>4</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-15 05:12:26</t>
+          <t>2026-08-20 03:50:27</t>
         </is>
       </c>
     </row>
@@ -3368,23 +3368,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F4689%2F&amp;fileName=DhJDFkOej1a5nzvq_5o2Gfgu1E5gKw3-.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E106" t="n">
         <v>4</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-15 05:30:28</t>
+          <t>2026-08-20 03:50:27</t>
         </is>
       </c>
     </row>
@@ -3396,23 +3396,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E107" t="n">
         <v>4</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-15 06:37:49</t>
+          <t>2026-08-20 03:50:32</t>
         </is>
       </c>
     </row>
@@ -3424,23 +3424,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E108" t="n">
         <v>4</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-15 06:40:10</t>
+          <t>2026-08-20 03:50:33</t>
         </is>
       </c>
     </row>
@@ -3452,23 +3452,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E109" t="n">
         <v>4</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-15 06:43:34</t>
+          <t>2026-08-20 03:50:38</t>
         </is>
       </c>
     </row>
@@ -3480,23 +3480,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E110" t="n">
         <v>4</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-15 06:45:51</t>
+          <t>2026-08-20 03:50:39</t>
         </is>
       </c>
     </row>
@@ -3508,23 +3508,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E111" t="n">
         <v>4</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-15 06:48:03</t>
+          <t>2026-08-20 03:51:13</t>
         </is>
       </c>
     </row>
@@ -3536,23 +3536,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E112" t="n">
         <v>4</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-15 06:50:06</t>
+          <t>2026-08-20 03:51:48</t>
         </is>
       </c>
     </row>
@@ -3564,23 +3564,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2467</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E113" t="n">
         <v>4</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-15 09:39:30</t>
+          <t>2026-08-20 03:52:23</t>
         </is>
       </c>
     </row>
@@ -3592,23 +3592,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2437</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E114" t="n">
         <v>4</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-15 10:13:13</t>
+          <t>2026-08-20 03:52:57</t>
         </is>
       </c>
     </row>
@@ -3620,23 +3620,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E115" t="n">
         <v>4</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-15 14:50:51</t>
+          <t>2026-08-20 03:53:16</t>
         </is>
       </c>
     </row>
@@ -3648,23 +3648,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E116" t="n">
         <v>4</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-15 14:55:36</t>
+          <t>2026-08-20 03:53:16</t>
         </is>
       </c>
     </row>
@@ -3676,23 +3676,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E117" t="n">
         <v>4</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-15 14:58:56</t>
+          <t>2026-08-20 03:53:21</t>
         </is>
       </c>
     </row>
@@ -3704,23 +3704,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E118" t="n">
         <v>4</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-15 15:01:43</t>
+          <t>2026-08-20 03:53:22</t>
         </is>
       </c>
     </row>
@@ -3732,23 +3732,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E119" t="n">
         <v>4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-15 15:07:57</t>
+          <t>2026-08-20 03:53:56</t>
         </is>
       </c>
     </row>
@@ -3760,23 +3760,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E120" t="n">
         <v>4</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-15 15:10:49</t>
+          <t>2026-08-20 03:54:31</t>
         </is>
       </c>
     </row>
@@ -3788,23 +3788,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E121" t="n">
         <v>4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-15 15:14:00</t>
+          <t>2026-08-20 03:55:05</t>
         </is>
       </c>
     </row>
@@ -3816,23 +3816,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E122" t="n">
         <v>4</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-15 15:16:39</t>
+          <t>2026-08-20 03:55:40</t>
         </is>
       </c>
     </row>
@@ -3844,23 +3844,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E123" t="n">
         <v>4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-15 15:19:58</t>
+          <t>2026-08-20 03:55:55</t>
         </is>
       </c>
     </row>
@@ -3872,23 +3872,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E124" t="n">
         <v>4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-15 15:22:27</t>
+          <t>2026-08-20 03:55:56</t>
         </is>
       </c>
     </row>
@@ -3900,23 +3900,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E125" t="n">
         <v>4</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-15 15:24:56</t>
+          <t>2026-08-20 03:56:01</t>
         </is>
       </c>
     </row>
@@ -3928,23 +3928,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E126" t="n">
         <v>4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-15 15:28:12</t>
+          <t>2026-08-20 03:56:01</t>
         </is>
       </c>
     </row>
@@ -3956,23 +3956,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E127" t="n">
         <v>4</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-15 15:31:08</t>
+          <t>2026-08-20 03:56:06</t>
         </is>
       </c>
     </row>
@@ -3984,23 +3984,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E128" t="n">
         <v>4</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-15 15:34:01</t>
+          <t>2026-08-20 03:56:07</t>
         </is>
       </c>
     </row>
@@ -4012,23 +4012,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E129" t="n">
         <v>4</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-15 15:37:03</t>
+          <t>2026-08-20 03:56:12</t>
         </is>
       </c>
     </row>
@@ -4040,23 +4040,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E130" t="n">
         <v>4</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-15 15:39:36</t>
+          <t>2026-08-20 03:56:13</t>
         </is>
       </c>
     </row>
@@ -4068,23 +4068,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E131" t="n">
         <v>4</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-15 15:43:10</t>
+          <t>2026-08-20 03:56:47</t>
         </is>
       </c>
     </row>
@@ -4096,23 +4096,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E132" t="n">
         <v>4</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-15 15:46:00</t>
+          <t>2026-08-20 03:57:22</t>
         </is>
       </c>
     </row>
@@ -4124,23 +4124,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E133" t="n">
         <v>4</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-15 15:49:26</t>
+          <t>2026-08-20 03:57:56</t>
         </is>
       </c>
     </row>
@@ -4152,23 +4152,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E134" t="n">
         <v>4</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-15 15:52:20</t>
+          <t>2026-08-20 03:58:30</t>
         </is>
       </c>
     </row>
@@ -4180,23 +4180,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E135" t="n">
         <v>4</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-15 15:54:51</t>
+          <t>2026-08-20 03:58:46</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-15 15:58:20</t>
+          <t>2026-08-20 04:00:29</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-15 16:01:11</t>
+          <t>2026-08-20 04:02:45</t>
         </is>
       </c>
     </row>
@@ -4264,23 +4264,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E138" t="n">
         <v>4</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-15 16:04:28</t>
+          <t>2026-08-20 04:03:19</t>
         </is>
       </c>
     </row>
@@ -4292,23 +4292,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E139" t="n">
         <v>4</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-15 16:07:24</t>
+          <t>2026-08-20 04:03:48</t>
         </is>
       </c>
     </row>
@@ -4320,23 +4320,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E140" t="n">
         <v>4</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-15 16:10:36</t>
+          <t>2026-08-20 04:03:56</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-15 16:15:10</t>
+          <t>2026-08-20 04:06:48</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-15 16:23:36</t>
+          <t>2026-08-20 04:08:54</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-15 16:26:17</t>
+          <t>2026-08-20 04:11:02</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-15 16:29:37</t>
+          <t>2026-08-20 04:13:12</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-15 16:33:02</t>
+          <t>2026-08-20 04:15:28</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-15 16:37:15</t>
+          <t>2026-08-20 04:17:44</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-15 16:40:35</t>
+          <t>2026-08-20 04:20:56</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-15 16:44:05</t>
+          <t>2026-08-20 04:22:57</t>
         </is>
       </c>
     </row>
@@ -4572,23 +4572,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>4</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-15 16:46:29</t>
+          <t>2026-08-20 04:25:14</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-15 16:49:38</t>
+          <t>2026-08-20 04:27:30</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-15 16:53:10</t>
+          <t>2026-08-20 04:29:46</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-15 16:56:41</t>
+          <t>2026-08-20 04:32:03</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-15 17:00:03</t>
+          <t>2026-08-20 04:34:08</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-15 17:04:51</t>
+          <t>2026-08-20 04:36:25</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-15 17:09:04</t>
+          <t>2026-08-20 04:38:41</t>
         </is>
       </c>
     </row>
@@ -4768,23 +4768,23 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>4</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-15 17:14:21</t>
+          <t>2026-08-20 04:40:57</t>
         </is>
       </c>
     </row>
@@ -4796,23 +4796,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/pagina/view/13?slug=sobre-a-lai-lei-de-acesso-a-informacao</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>4</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-15 17:14:39</t>
+          <t>2026-08-20 04:43:14</t>
         </is>
       </c>
     </row>
@@ -4824,23 +4824,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-15 17:27:44</t>
+          <t>2026-08-20 04:45:30</t>
         </is>
       </c>
     </row>
@@ -4852,23 +4852,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-15 17:28:19</t>
+          <t>2026-08-20 04:47:46</t>
         </is>
       </c>
     </row>
@@ -4880,23 +4880,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-15 17:28:53</t>
+          <t>2026-08-20 04:49:59</t>
         </is>
       </c>
     </row>
@@ -4908,23 +4908,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-15 17:29:27</t>
+          <t>2026-08-20 04:52:11</t>
         </is>
       </c>
     </row>
@@ -4936,23 +4936,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-15 17:29:49</t>
+          <t>2026-08-20 04:54:28</t>
         </is>
       </c>
     </row>
@@ -4964,23 +4964,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-15 17:29:56</t>
+          <t>2026-08-20 04:56:44</t>
         </is>
       </c>
     </row>
@@ -4992,23 +4992,23 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-15 17:29:57</t>
+          <t>2026-08-20 04:59:00</t>
         </is>
       </c>
     </row>
@@ -5020,23 +5020,23 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-15 17:31:33</t>
+          <t>2026-08-20 05:01:17</t>
         </is>
       </c>
     </row>
@@ -5048,23 +5048,23 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-15 17:31:55</t>
+          <t>2026-08-20 05:03:33</t>
         </is>
       </c>
     </row>
@@ -5076,23 +5076,23 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-15 17:32:32</t>
+          <t>2026-08-20 05:05:43</t>
         </is>
       </c>
     </row>
@@ -5104,23 +5104,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-15 17:33:06</t>
+          <t>2026-08-20 05:07:56</t>
         </is>
       </c>
     </row>
@@ -5132,23 +5132,23 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-15 17:33:38</t>
+          <t>2026-08-20 05:10:12</t>
         </is>
       </c>
     </row>
@@ -5160,23 +5160,23 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-15 17:34:00</t>
+          <t>2026-08-20 05:12:28</t>
         </is>
       </c>
     </row>
@@ -5188,23 +5188,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-15 17:34:05</t>
+          <t>2026-08-20 05:14:45</t>
         </is>
       </c>
     </row>
@@ -5216,23 +5216,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-15 17:34:06</t>
+          <t>2026-08-20 05:17:01</t>
         </is>
       </c>
     </row>
@@ -5244,23 +5244,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-15 17:34:41</t>
+          <t>2026-08-20 05:19:17</t>
         </is>
       </c>
     </row>
@@ -5272,23 +5272,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-15 17:35:15</t>
+          <t>2026-08-20 05:21:34</t>
         </is>
       </c>
     </row>
@@ -5300,23 +5300,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-15 17:35:49</t>
+          <t>2026-08-20 05:23:42</t>
         </is>
       </c>
     </row>
@@ -5328,23 +5328,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-15 17:36:07</t>
+          <t>2026-08-20 05:25:58</t>
         </is>
       </c>
     </row>
@@ -5356,23 +5356,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-15 17:36:08</t>
+          <t>2026-08-20 05:28:08</t>
         </is>
       </c>
     </row>
@@ -5384,23 +5384,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-15 17:36:42</t>
+          <t>2026-08-20 05:30:24</t>
         </is>
       </c>
     </row>
@@ -5412,23 +5412,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-15 17:37:17</t>
+          <t>2026-08-20 05:32:40</t>
         </is>
       </c>
     </row>
@@ -5440,23 +5440,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-15 17:37:51</t>
+          <t>2026-08-20 05:34:56</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5480,11 +5480,11 @@
         <v>500</v>
       </c>
       <c r="E181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-08-15 17:38:12</t>
+          <t>2026-08-20 05:35:35</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5508,11 +5508,11 @@
         <v>500</v>
       </c>
       <c r="E182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-15 17:38:17</t>
+          <t>2026-08-20 05:36:01</t>
         </is>
       </c>
     </row>
@@ -5524,23 +5524,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-15 17:38:18</t>
+          <t>2026-08-20 05:38:18</t>
         </is>
       </c>
     </row>
@@ -5552,23 +5552,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-08-15 17:38:52</t>
+          <t>2026-08-20 05:40:34</t>
         </is>
       </c>
     </row>
@@ -5580,23 +5580,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-08-15 17:39:27</t>
+          <t>2026-08-20 05:42:50</t>
         </is>
       </c>
     </row>
@@ -5608,23 +5608,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-08-15 17:39:58</t>
+          <t>2026-08-20 05:44:54</t>
         </is>
       </c>
     </row>
@@ -5636,23 +5636,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-08-15 17:40:18</t>
+          <t>2026-08-20 05:47:03</t>
         </is>
       </c>
     </row>
@@ -5664,23 +5664,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-08-15 17:40:23</t>
+          <t>2026-08-20 05:49:19</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-15 17:40:24</t>
+          <t>2026-08-20 05:49:54</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-15 17:40:58</t>
+          <t>2026-08-20 05:50:17</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-15 17:41:33</t>
+          <t>2026-08-20 05:50:41</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-15 17:42:05</t>
+          <t>2026-08-20 05:51:16</t>
         </is>
       </c>
     </row>
@@ -5804,23 +5804,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E193" t="n">
         <v>5</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-15 17:51:17</t>
+          <t>2026-08-20 05:51:50</t>
         </is>
       </c>
     </row>
@@ -5832,23 +5832,23 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E194" t="n">
         <v>5</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-08-15 19:31:19</t>
+          <t>2026-08-20 05:52:25</t>
         </is>
       </c>
     </row>
@@ -5860,23 +5860,23 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E195" t="n">
         <v>5</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-08-15 19:33:35</t>
+          <t>2026-08-20 05:53:00</t>
         </is>
       </c>
     </row>
@@ -5888,23 +5888,23 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2629</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E196" t="n">
         <v>5</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-08-15 21:38:25</t>
+          <t>2026-08-20 05:53:11</t>
         </is>
       </c>
     </row>
@@ -5916,23 +5916,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2704</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E197" t="n">
         <v>5</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-08-16 00:19:47</t>
+          <t>2026-08-20 05:53:11</t>
         </is>
       </c>
     </row>
@@ -5944,23 +5944,23 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2701</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E198" t="n">
         <v>5</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-08-16 00:24:03</t>
+          <t>2026-08-20 05:53:16</t>
         </is>
       </c>
     </row>
@@ -5972,23 +5972,23 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2696</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E199" t="n">
         <v>5</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-16 00:24:19</t>
+          <t>2026-08-20 05:53:17</t>
         </is>
       </c>
     </row>
@@ -6000,23 +6000,23 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2696</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E200" t="n">
         <v>5</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-16 00:24:20</t>
+          <t>2026-08-20 05:53:22</t>
         </is>
       </c>
     </row>
@@ -6028,23 +6028,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2699</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E201" t="n">
         <v>5</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-16 00:25:46</t>
+          <t>2026-08-20 05:53:22</t>
         </is>
       </c>
     </row>
@@ -6056,23 +6056,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4790%2F&amp;fileName=S-5a79hl6E2wdPJbdt2mV69ZElOljS5i.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E202" t="n">
         <v>5</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-16 00:28:21</t>
+          <t>2026-08-20 05:53:57</t>
         </is>
       </c>
     </row>
@@ -6084,23 +6084,23 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2695</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E203" t="n">
         <v>5</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-16 00:28:23</t>
+          <t>2026-08-20 05:54:31</t>
         </is>
       </c>
     </row>
@@ -6112,23 +6112,23 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2695</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E204" t="n">
         <v>5</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-16 00:28:26</t>
+          <t>2026-08-20 05:55:05</t>
         </is>
       </c>
     </row>
@@ -6140,23 +6140,23 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4785%2F&amp;fileName=ABgO3MmorlJmlKpE1JYt4kOV-R0FRzdW.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E205" t="n">
         <v>5</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-08-16 00:28:28</t>
+          <t>2026-08-20 05:55:40</t>
         </is>
       </c>
     </row>
@@ -6168,23 +6168,23 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2693</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E206" t="n">
         <v>5</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-16 00:28:30</t>
+          <t>2026-08-20 05:55:53</t>
         </is>
       </c>
     </row>
@@ -6196,23 +6196,23 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2671</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E207" t="n">
         <v>5</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-08-16 00:30:32</t>
+          <t>2026-08-20 05:55:54</t>
         </is>
       </c>
     </row>
@@ -6224,23 +6224,23 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4717%2F&amp;fileName=8lJ9zH6oQlTMgNV5WYswielFpU-Jd7-h.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E208" t="n">
         <v>5</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-16 00:32:07</t>
+          <t>2026-08-20 05:56:00</t>
         </is>
       </c>
     </row>
@@ -6252,23 +6252,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4716%2F&amp;fileName=UXgIPCyyW4CTzlqHTFbev87gVLm3tL-J.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E209" t="n">
         <v>5</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-16 00:32:38</t>
+          <t>2026-08-20 05:56:00</t>
         </is>
       </c>
     </row>
@@ -6280,23 +6280,23 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2673</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E210" t="n">
         <v>5</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-08-16 00:32:42</t>
+          <t>2026-08-20 05:56:35</t>
         </is>
       </c>
     </row>
@@ -6308,23 +6308,23 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F4730%2F&amp;fileName=sBIlP8G4kRim6DjdOQbdmK0YAiYOwweF.pdf</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E211" t="n">
         <v>5</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-08-16 00:32:47</t>
+          <t>2026-08-20 05:57:09</t>
         </is>
       </c>
     </row>
@@ -6336,23 +6336,23 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2651</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E212" t="n">
         <v>5</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-16 00:47:51</t>
+          <t>2026-08-20 05:57:44</t>
         </is>
       </c>
     </row>
@@ -6364,23 +6364,23 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2646</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E213" t="n">
         <v>5</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-16 00:49:36</t>
+          <t>2026-08-20 05:58:18</t>
         </is>
       </c>
     </row>
@@ -6392,23 +6392,23 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2645</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E214" t="n">
         <v>5</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-16 00:49:48</t>
+          <t>2026-08-20 05:58:34</t>
         </is>
       </c>
     </row>
@@ -6420,23 +6420,23 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2644</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E215" t="n">
         <v>5</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-16 00:50:28</t>
+          <t>2026-08-20 05:58:34</t>
         </is>
       </c>
     </row>
@@ -6448,23 +6448,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2644</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E216" t="n">
         <v>5</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-16 00:50:29</t>
+          <t>2026-08-20 05:58:40</t>
         </is>
       </c>
     </row>
@@ -6476,23 +6476,23 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2643</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E217" t="n">
         <v>5</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-16 00:50:42</t>
+          <t>2026-08-20 05:58:40</t>
         </is>
       </c>
     </row>
@@ -6504,23 +6504,23 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E218" t="n">
         <v>5</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-16 04:43:23</t>
+          <t>2026-08-20 05:59:15</t>
         </is>
       </c>
     </row>
@@ -6532,23 +6532,23 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E219" t="n">
         <v>5</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-08-16 04:48:20</t>
+          <t>2026-08-20 05:59:49</t>
         </is>
       </c>
     </row>
@@ -6560,23 +6560,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E220" t="n">
         <v>5</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-16 04:51:09</t>
+          <t>2026-08-20 06:00:24</t>
         </is>
       </c>
     </row>
@@ -6588,23 +6588,23 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E221" t="n">
         <v>5</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-16 04:54:33</t>
+          <t>2026-08-20 06:01:00</t>
         </is>
       </c>
     </row>
@@ -6616,23 +6616,23 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E222" t="n">
         <v>5</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-16 05:00:42</t>
+          <t>2026-08-20 06:01:15</t>
         </is>
       </c>
     </row>
@@ -6644,23 +6644,23 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E223" t="n">
         <v>5</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-16 05:03:26</t>
+          <t>2026-08-20 06:01:15</t>
         </is>
       </c>
     </row>
@@ -6672,23 +6672,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E224" t="n">
         <v>5</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-16 05:06:38</t>
+          <t>2026-08-20 06:01:20</t>
         </is>
       </c>
     </row>
@@ -6700,23 +6700,23 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E225" t="n">
         <v>5</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-16 05:09:13</t>
+          <t>2026-08-20 06:01:21</t>
         </is>
       </c>
     </row>
@@ -6728,23 +6728,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E226" t="n">
         <v>5</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-16 05:12:13</t>
+          <t>2026-08-20 06:01:55</t>
         </is>
       </c>
     </row>
@@ -6756,23 +6756,23 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
+          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E227" t="n">
         <v>5</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-16 05:15:31</t>
+          <t>2026-08-20 06:02:30</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-16 05:18:11</t>
+          <t>2026-08-20 06:04:47</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-16 05:21:31</t>
+          <t>2026-08-20 06:07:03</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
+          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-16 05:24:31</t>
+          <t>2026-08-20 06:09:19</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-16 05:27:33</t>
+          <t>2026-08-20 06:22:16</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-16 05:30:36</t>
+          <t>2026-08-20 06:24:33</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-16 05:33:25</t>
+          <t>2026-08-20 06:26:43</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-16 05:36:38</t>
+          <t>2026-08-20 06:28:51</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-16 05:39:15</t>
+          <t>2026-08-20 06:31:07</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-16 05:42:10</t>
+          <t>2026-08-20 06:33:19</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-16 05:45:25</t>
+          <t>2026-08-20 06:35:35</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-16 05:48:27</t>
+          <t>2026-08-20 06:37:51</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-16 05:51:50</t>
+          <t>2026-08-20 06:40:08</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2026-08-16 05:54:52</t>
+          <t>2026-08-20 06:42:11</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2026-08-16 05:58:15</t>
+          <t>2026-08-20 06:44:26</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2026-08-16 06:01:13</t>
+          <t>2026-08-20 06:46:42</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2026-08-16 06:03:51</t>
+          <t>2026-08-20 06:48:58</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2026-08-16 06:09:29</t>
+          <t>2026-08-20 06:51:14</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2026-08-16 06:17:26</t>
+          <t>2026-08-20 06:53:31</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2026-08-16 06:21:06</t>
+          <t>2026-08-20 06:55:43</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-08-16 06:24:33</t>
+          <t>2026-08-20 06:57:57</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:31</t>
+          <t>2026-08-20 07:00:03</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:45</t>
+          <t>2026-08-20 07:02:20</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-08-16 06:35:14</t>
+          <t>2026-08-20 07:04:36</t>
         </is>
       </c>
     </row>
@@ -7428,23 +7428,23 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E251" t="n">
         <v>5</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-08-16 06:38:16</t>
+          <t>2026-08-20 07:06:52</t>
         </is>
       </c>
     </row>
@@ -7456,23 +7456,23 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
         <v>5</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-08-16 06:38:37</t>
+          <t>2026-08-20 07:09:09</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-08-16 06:41:40</t>
+          <t>2026-08-20 07:11:25</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-16 06:44:44</t>
+          <t>2026-08-20 07:13:32</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-08-16 06:48:00</t>
+          <t>2026-08-20 07:15:49</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-16 06:51:05</t>
+          <t>2026-08-20 07:18:05</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-16 06:55:23</t>
+          <t>2026-08-20 07:20:21</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-08-16 06:59:33</t>
+          <t>2026-08-20 07:22:37</t>
         </is>
       </c>
     </row>
@@ -7652,23 +7652,23 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E259" t="n">
         <v>5</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2026-08-16 07:00:16</t>
+          <t>2026-08-20 07:24:53</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fnoticia%2F2515%2F&amp;fileName=KNqDTWHas_PUi2G77U45744qPToGyks-.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:26</t>
+          <t>2026-08-20 07:27:10</t>
         </is>
       </c>
     </row>
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/noticia/exportar-csv?id=60</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-08-16 10:24:05</t>
+          <t>2026-08-20 07:29:19</t>
         </is>
       </c>
     </row>
@@ -7736,23 +7736,23 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F3316%2F&amp;fileName=Afjy5wpfMIhSJL1NmftWF0WHcrrcTOWi.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D262" t="n">
         <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-08-16 12:17:50</t>
+          <t>2026-08-20 07:31:35</t>
         </is>
       </c>
     </row>
@@ -7764,23 +7764,23 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/formulario/view/4/fale-conosco-2</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-08-16 13:49:44</t>
+          <t>2026-08-20 07:33:51</t>
         </is>
       </c>
     </row>
@@ -7792,23 +7792,23 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/conta</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E264" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-08-16 13:50:13</t>
+          <t>2026-08-20 07:34:52</t>
         </is>
       </c>
     </row>
@@ -7820,23 +7820,23 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/conta/logout</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E265" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-08-16 13:50:48</t>
+          <t>2026-08-20 07:37:05</t>
         </is>
       </c>
     </row>
@@ -7848,23 +7848,23 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2063</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D266" t="n">
         <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2026-08-16 20:13:48</t>
+          <t>2026-08-20 07:39:22</t>
         </is>
       </c>
     </row>
@@ -7876,23 +7876,23 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2062</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D267" t="n">
         <v>0</v>
       </c>
       <c r="E267" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-08-16 20:35:04</t>
+          <t>2026-08-20 07:41:38</t>
         </is>
       </c>
     </row>
@@ -7904,23 +7904,23 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=2053</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D268" t="n">
         <v>0</v>
       </c>
       <c r="E268" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-08-16 21:45:40</t>
+          <t>2026-08-20 07:43:54</t>
         </is>
       </c>
     </row>
@@ -7932,23 +7932,23 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F2548%2F&amp;fileName=88DHZz_EzdewK_OA7biNC-OU5XLTGN2Z.pdf</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D269" t="n">
         <v>0</v>
       </c>
       <c r="E269" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2026-08-16 21:52:02</t>
+          <t>2026-08-20 07:46:10</t>
         </is>
       </c>
     </row>
@@ -7960,23 +7960,23 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2047</t>
+          <t>https://saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D270" t="n">
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2026-08-16 22:36:17</t>
+          <t>2026-08-20 07:48:27</t>
         </is>
       </c>
     </row>
@@ -7988,12 +7988,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/legislacao/exportar-csv?id=2258</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2026-08-16 23:44:12</t>
+          <t>2026-08-20 07:54:57</t>
         </is>
       </c>
     </row>
@@ -8016,23 +8016,23 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E272" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2026-08-17 01:13:22</t>
+          <t>2026-08-20 07:55:51</t>
         </is>
       </c>
     </row>
@@ -8044,23 +8044,23 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/cdn-cgi/l/email-protection</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E273" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-08-17 01:13:28</t>
+          <t>2026-08-20 07:56:26</t>
         </is>
       </c>
     </row>
@@ -8072,23 +8072,23 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-08-17 01:16:23</t>
+          <t>2026-08-20 08:02:25</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/pagina/impressao?id=4</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3911%2F&amp;fileName=X5KqhAne5I0dx9A0D1_0bwa0YMuF7-dx.pdf</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8112,11 +8112,11 @@
         <v>0</v>
       </c>
       <c r="E275" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2026-08-17 01:19:43</t>
+          <t>2026-08-20 08:04:41</t>
         </is>
       </c>
     </row>
@@ -8128,23 +8128,23 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/conta/index</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2026-08-17 01:34:16</t>
+          <t>2026-08-20 08:06:57</t>
         </is>
       </c>
     </row>
@@ -8156,23 +8156,23 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://saojeronimodaserra.pr.gov.br/noticia/exportar-txt?id=107</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3914%2F&amp;fileName=KEx8tB0aL4K7Gg1bjGKZVM-JUhRPoRIk.pdf</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D277" t="n">
         <v>0</v>
       </c>
       <c r="E277" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2026-08-17 02:00:49</t>
+          <t>2026-08-20 08:09:14</t>
         </is>
       </c>
     </row>
@@ -8184,23 +8184,23 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Flegislacao%2F261%2F&amp;fileName=Lj_f0GzZ8ezXqD908-JXSf1euHVZCLjL.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D278" t="n">
         <v>0</v>
       </c>
       <c r="E278" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>2026-08-17 02:52:58</t>
+          <t>2026-08-20 08:11:23</t>
         </is>
       </c>
     </row>
@@ -8212,23 +8212,23 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2091/resolucao-n-0012023</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E279" t="n">
         <v>8</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>2026-08-17 08:41:48</t>
+          <t>2026-08-20 08:13:40</t>
         </is>
       </c>
     </row>
@@ -8240,23 +8240,23 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2090/resolucao-n-0022023</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fcontratacao%2F3915%2F&amp;fileName=GHzfksmX4p2K7INFhclMghFnvxVuUti2.pdf</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>HTTP_500</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="E280" t="n">
         <v>8</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>2026-08-17 08:42:22</t>
+          <t>2026-08-20 08:14:21</t>
         </is>
       </c>
     </row>
@@ -8268,23 +8268,23 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/legislacao/view/2089/resolucao-n-0032023</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>2026-08-17 08:42:57</t>
+          <t>2026-08-20 08:17:12</t>
         </is>
       </c>
     </row>
@@ -8296,23 +8296,23 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F2727%2F&amp;fileName=TYB-5uHV7fW2KhAe1KgYePWjyjJuQ7BR.pdf</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E282" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2026-08-17 08:45:17</t>
+          <t>2026-08-20 08:19:28</t>
         </is>
       </c>
     </row>
@@ -8324,23 +8324,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=245</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E283" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>2026-08-17 08:45:43</t>
+          <t>2026-08-20 08:31:36</t>
         </is>
       </c>
     </row>
@@ -8352,23 +8352,23 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3405%2F&amp;fileName=pmFqq6BSkiCnJx0AQLWaAfZzCQ1pDBfM.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=243</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E284" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>2026-08-17 08:45:48</t>
+          <t>2026-08-20 08:34:27</t>
         </is>
       </c>
     </row>
@@ -8380,23 +8380,23 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdepartamento%2F3151%2F&amp;fileName=lu3xk3zyyNqMPh6jBy1EAZmiYDalzW5H.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=241</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D285" t="n">
         <v>0</v>
       </c>
       <c r="E285" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-08-17 08:50:04</t>
+          <t>2026-08-20 08:36:39</t>
         </is>
       </c>
     </row>
@@ -8408,23 +8408,23 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/departamento/exportar-csv?id=16</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=240</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D286" t="n">
         <v>0</v>
       </c>
       <c r="E286" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-08-17 08:56:59</t>
+          <t>2026-08-20 08:39:01</t>
         </is>
       </c>
     </row>
@@ -8436,23 +8436,23 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4256%2F&amp;fileName=FuG4kRaMKrwxbGzvLUKFLaXZOzFW4u9U.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=234</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D287" t="n">
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2026-08-17 09:42:48</t>
+          <t>2026-08-20 08:41:27</t>
         </is>
       </c>
     </row>
@@ -8464,23 +8464,23 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F4258%2F&amp;fileName=4GK1v_Rs0iZLZOoCpvwdBcMlfu4Z1I0F.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=233</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D288" t="n">
         <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-08-17 09:47:14</t>
+          <t>2026-08-20 08:43:43</t>
         </is>
       </c>
     </row>
@@ -8492,23 +8492,23 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fentidade%2F25%2F&amp;fileName=Ql1LkQPoot0af2Tf_Hqjn5PaPTb-fvHW.pdf</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=232</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D289" t="n">
         <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2026-08-17 11:28:11</t>
+          <t>2026-08-20 08:45:59</t>
         </is>
       </c>
     </row>
@@ -8520,23 +8520,23 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/contato/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=230</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E290" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>2026-08-17 11:33:46</t>
+          <t>2026-08-20 08:49:17</t>
         </is>
       </c>
     </row>
@@ -8548,23 +8548,23 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=229</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>2026-08-17 12:23:55</t>
+          <t>2026-08-20 08:51:33</t>
         </is>
       </c>
     </row>
@@ -8576,23 +8576,23 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=228</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E292" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>2026-08-17 12:24:05</t>
+          <t>2026-08-20 08:53:49</t>
         </is>
       </c>
     </row>
@@ -8604,23 +8604,23 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/site/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=225</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E293" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-08-17 12:24:06</t>
+          <t>2026-08-20 08:56:06</t>
         </is>
       </c>
     </row>
@@ -8632,23 +8632,23 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=224</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>2026-08-17 12:24:39</t>
+          <t>2026-08-20 08:58:19</t>
         </is>
       </c>
     </row>
@@ -8660,23 +8660,2011 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>http://www.saojeronimodaserra.pr.gov.br/ouvidoria/relatorio/ouvidoria@saojeronimodaserra.pr.gov.br</t>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=223</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E295" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-08-17 12:24:45</t>
+          <t>2026-08-20 09:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=222</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>9</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:03:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=221</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>9</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:06:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=220</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>9</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:08:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=219</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>9</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:11:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=218</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>9</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=217</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>9</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=216</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>9</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=215</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>9</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:20:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=214</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>9</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:23:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=213</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>9</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:27:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=212</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>9</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:29:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=211</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>9</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:31:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/exportar-txt?id=211</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>9</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:32:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=210</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>9</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:33:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=207</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>9</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:35:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=202</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>9</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:39:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=201</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>9</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:42:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=200</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>9</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:44:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=199</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>9</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=197</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>9</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=196</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>9</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:50:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>9</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=195</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>500</v>
+      </c>
+      <c r="E318" t="n">
+        <v>9</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:53:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=193</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>500</v>
+      </c>
+      <c r="E319" t="n">
+        <v>9</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:54:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=192</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>9</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=191</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>9</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:58:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=190</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>9</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:00:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=189</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>9</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:02:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=187</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>9</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:04:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/noticia/impressao?id=184</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>9</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:07:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=765</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>9</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:07:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>500</v>
+      </c>
+      <c r="E327" t="n">
+        <v>10</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:07:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3426%2F&amp;fileName=eytM84Z2E0prElR3xrzqYeOEJ1P0jfhc.pdf</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>500</v>
+      </c>
+      <c r="E328" t="n">
+        <v>10</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:08:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>500</v>
+      </c>
+      <c r="E329" t="n">
+        <v>10</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>500</v>
+      </c>
+      <c r="E330" t="n">
+        <v>10</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3542%2F&amp;fileName=Hcc1xEhF_hcTo8Qu5ON5QkkRoeWKzyib.pdf</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>500</v>
+      </c>
+      <c r="E331" t="n">
+        <v>10</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:09:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>500</v>
+      </c>
+      <c r="E332" t="n">
+        <v>10</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3932%2F&amp;fileName=TroHHZofOdlZNiTe1PosLbL4PP9_f_MW.pdf</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>500</v>
+      </c>
+      <c r="E333" t="n">
+        <v>10</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:10:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>500</v>
+      </c>
+      <c r="E334" t="n">
+        <v>10</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:10:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3406%2F&amp;fileName=qHMQxwTDBPU1gh6dWJrJJHiWLAQykGSb.pdf</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>500</v>
+      </c>
+      <c r="E335" t="n">
+        <v>10</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>500</v>
+      </c>
+      <c r="E336" t="n">
+        <v>10</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>500</v>
+      </c>
+      <c r="E337" t="n">
+        <v>10</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:12:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3407%2F&amp;fileName=OID-OtXDLxve5k9E7h0gDAcXbUutukEp.pdf</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>10</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:12:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>500</v>
+      </c>
+      <c r="E339" t="n">
+        <v>10</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3408%2F&amp;fileName=MgSLbu2PmMTn66YqLTjFa-bJmTlQGiQu.pdf</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>500</v>
+      </c>
+      <c r="E340" t="n">
+        <v>10</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:12:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>500</v>
+      </c>
+      <c r="E341" t="n">
+        <v>10</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:13:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>10</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:13:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3409%2F&amp;fileName=opTWHnYMd1V5ExF_wRSSMijlueqAJiJS.pdf</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>500</v>
+      </c>
+      <c r="E343" t="n">
+        <v>10</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>500</v>
+      </c>
+      <c r="E344" t="n">
+        <v>10</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:14:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>500</v>
+      </c>
+      <c r="E345" t="n">
+        <v>10</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:14:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3410%2F&amp;fileName=xWs8-ppgPyQLDcbgQC0ScBC9GoeDUFv1.pdf</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>500</v>
+      </c>
+      <c r="E346" t="n">
+        <v>10</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:14:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>500</v>
+      </c>
+      <c r="E347" t="n">
+        <v>10</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>500</v>
+      </c>
+      <c r="E348" t="n">
+        <v>10</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:15:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3411%2F&amp;fileName=I19EKZUftPj3z-7ZPAxcZsyUAFeM9Iw6.pdf</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>10</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>500</v>
+      </c>
+      <c r="E350" t="n">
+        <v>10</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3412%2F&amp;fileName=PiXnc-Marxm5m51TrtP6VFZNN_Vglcp4.pdf</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>500</v>
+      </c>
+      <c r="E351" t="n">
+        <v>10</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>500</v>
+      </c>
+      <c r="E352" t="n">
+        <v>10</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>10</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>500</v>
+      </c>
+      <c r="E354" t="n">
+        <v>10</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3413%2F&amp;fileName=GJ7eH6jLhQhs7P5X8g0lEQmlJPaDWLOl.pdf</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>500</v>
+      </c>
+      <c r="E355" t="n">
+        <v>10</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:17:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>500</v>
+      </c>
+      <c r="E356" t="n">
+        <v>10</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:17:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3414%2F&amp;fileName=YPioXmywRUdSnlgWZrNRhUcczcM9tMcW.pdf</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>500</v>
+      </c>
+      <c r="E357" t="n">
+        <v>10</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>500</v>
+      </c>
+      <c r="E358" t="n">
+        <v>10</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:18:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3415%2F&amp;fileName=AEu-NNLJ69yOeJ2xDyr0hb-7KlKbFT2K.pdf</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>500</v>
+      </c>
+      <c r="E359" t="n">
+        <v>10</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>500</v>
+      </c>
+      <c r="E360" t="n">
+        <v>10</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>500</v>
+      </c>
+      <c r="E361" t="n">
+        <v>10</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:19:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3416%2F&amp;fileName=-IZ7iyf9wNtYR3dqUfaPLcPCEM3n-v2N.pdf</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>500</v>
+      </c>
+      <c r="E362" t="n">
+        <v>10</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:19:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=txt&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>500</v>
+      </c>
+      <c r="E363" t="n">
+        <v>10</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:20:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>500</v>
+      </c>
+      <c r="E364" t="n">
+        <v>10</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>http://www.saojeronimodaserra.pr.gov.br/site/download?type=csv&amp;path=%2Fapp%2Ffrontend%2Fweb%2Fuploads%2Fdocumento%2F3417%2F&amp;fileName=vUnQezADTXxuvBf1i4Zy2P97iKzVyPup.pdf</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>10</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>saojeronimodaserra</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://www.saojeronimodaserra.pr.gov.br/legislacao/exportar-txt?id=246</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>10</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:22:11</t>
         </is>
       </c>
     </row>
